--- a/Data/Terminator_Strength-250423-2.xlsx
+++ b/Data/Terminator_Strength-250423-2.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uob-my.sharepoint.com/personal/zw24976_bristol_ac_uk/Documents/Documents/BCL/PhagePol_Terminators/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="83" documentId="8_{1743323C-19C1-43AB-8B8C-669E60D17429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC8D9CB2-A23C-4B06-8570-15F9F68B2F79}"/>
+  <xr:revisionPtr revIDLastSave="89" documentId="8_{1743323C-19C1-43AB-8B8C-669E60D17429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C15840E-1327-43B6-B3A8-56F61607CCAC}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{FAC3B235-24A1-4A8D-973B-F5D14E0CA428}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FAC3B235-24A1-4A8D-973B-F5D14E0CA428}"/>
   </bookViews>
   <sheets>
-    <sheet name="OD600" sheetId="1" r:id="rId1"/>
-    <sheet name="GFP" sheetId="3" r:id="rId2"/>
-    <sheet name="RFP" sheetId="4" r:id="rId3"/>
+    <sheet name="PlateMap" sheetId="5" r:id="rId1"/>
+    <sheet name="OD600" sheetId="1" r:id="rId2"/>
+    <sheet name="GFP" sheetId="3" r:id="rId3"/>
+    <sheet name="RFP" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7385" uniqueCount="5481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7489" uniqueCount="5585">
   <si>
     <t>Time</t>
   </si>
@@ -16489,6 +16490,318 @@
   </si>
   <si>
     <t>2634</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb1-lacO</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb1-tetO</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb1-G3T</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb1-G3Tr</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb1-20bp</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb1-20_lacO</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb1-20_tetO</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb1-20_G3T</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb1-20_G3Tr</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb8-lacO</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb8-tetO</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb8-G3T</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb8-G3Tr</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb8-20bp</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb8-20_lacO</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb8-20_tetO</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb8-20_G3T</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb8-20_G3Tr</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S2P11-lacO</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S2P11-tetO</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S2P11-G3T</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S2P11-G3Tr</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S2P11-20bp</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S2P11-20_lacO</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S2P11-20_tetO</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S2P11-20_G3T</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S2P11-20_G3Tr</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S1P00-lacO</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S1P00-tetO</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S1P00-G3T</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S1P00-G3Tr</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S1P00-20bp</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S1P00-20_lacO</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S1P00-20_tetO</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S1P00-20_G3T</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S1P00-20_G3Tr</t>
+  </si>
+  <si>
+    <t>0Cuma-50bp-lacO</t>
+  </si>
+  <si>
+    <t>0Cuma-50bp-tetO</t>
+  </si>
+  <si>
+    <t>0Cuma-50bp-G3T</t>
+  </si>
+  <si>
+    <t>0Cuma-50bp-G3Tr</t>
+  </si>
+  <si>
+    <t>0Cuma-50bp-20bp</t>
+  </si>
+  <si>
+    <t>0Cuma-50bp-20_lacO</t>
+  </si>
+  <si>
+    <t>0Cuma-50bp-20_tetO</t>
+  </si>
+  <si>
+    <t>0Cuma-50bp-20_G3T</t>
+  </si>
+  <si>
+    <t>0Cuma-50bp-20_G3Tr</t>
+  </si>
+  <si>
+    <t>0Cuma-RPU</t>
+  </si>
+  <si>
+    <t>0Cuma-AF</t>
+  </si>
+  <si>
+    <t>0Cuma-Blank</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb1-lacO</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb1-tetO</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb1-G3T</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb1-G3Tr</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb1-20bp</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb1-20_lacO</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb1-20_tetO</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb1-20_G3T</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb1-20_G3Tr</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb8-lacO</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb8-tetO</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb8-G3T</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb8-G3Tr</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb8-20bp</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb8-20_lacO</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb8-20_tetO</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb8-20_G3T</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb8-20_G3Tr</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S2P11-lacO</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S2P11-tetO</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S2P11-G3T</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S2P11-G3Tr</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S2P11-20bp</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S2P11-20_lacO</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S2P11-20_tetO</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S2P11-20_G3T</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S2P11-20_G3Tr</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S1P00-lacO</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S1P00-tetO</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S1P00-G3T</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S1P00-G3Tr</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S1P00-20bp</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S1P00-20_lacO</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S1P00-20_tetO</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S1P00-20_G3T</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S1P00-20_G3Tr</t>
+  </si>
+  <si>
+    <t>10Cuma-50bp-lacO</t>
+  </si>
+  <si>
+    <t>10Cuma-50bp-tetO</t>
+  </si>
+  <si>
+    <t>10Cuma-50bp-G3T</t>
+  </si>
+  <si>
+    <t>10Cuma-50bp-G3Tr</t>
+  </si>
+  <si>
+    <t>10Cuma-50bp-20bp</t>
+  </si>
+  <si>
+    <t>10Cuma-50bp-20_lacO</t>
+  </si>
+  <si>
+    <t>10Cuma-50bp-20_tetO</t>
+  </si>
+  <si>
+    <t>10Cuma-50bp-20_G3T</t>
+  </si>
+  <si>
+    <t>10Cuma-50bp-20_G3Tr</t>
+  </si>
+  <si>
+    <t>10Cuma-RPU</t>
+  </si>
+  <si>
+    <t>10Cuma-AF</t>
+  </si>
+  <si>
+    <t>10Cuma-Blank</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>H</t>
   </si>
 </sst>
 </file>
@@ -16897,6 +17210,382 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A2469A2-8072-42D6-99B6-ED05C84C2A7D}">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>2</v>
+      </c>
+      <c r="D1">
+        <v>3</v>
+      </c>
+      <c r="E1">
+        <v>4</v>
+      </c>
+      <c r="F1">
+        <v>5</v>
+      </c>
+      <c r="G1">
+        <v>6</v>
+      </c>
+      <c r="H1">
+        <v>7</v>
+      </c>
+      <c r="I1">
+        <v>8</v>
+      </c>
+      <c r="J1">
+        <v>9</v>
+      </c>
+      <c r="K1">
+        <v>10</v>
+      </c>
+      <c r="L1">
+        <v>11</v>
+      </c>
+      <c r="M1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>5577</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5481</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5482</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5483</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5484</v>
+      </c>
+      <c r="F2" t="s">
+        <v>5485</v>
+      </c>
+      <c r="G2" t="s">
+        <v>5486</v>
+      </c>
+      <c r="H2" t="s">
+        <v>5487</v>
+      </c>
+      <c r="I2" t="s">
+        <v>5488</v>
+      </c>
+      <c r="J2" t="s">
+        <v>5489</v>
+      </c>
+      <c r="K2" t="s">
+        <v>5490</v>
+      </c>
+      <c r="L2" t="s">
+        <v>5491</v>
+      </c>
+      <c r="M2" t="s">
+        <v>5492</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5578</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5493</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5494</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5495</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5496</v>
+      </c>
+      <c r="F3" t="s">
+        <v>5497</v>
+      </c>
+      <c r="G3" t="s">
+        <v>5498</v>
+      </c>
+      <c r="H3" t="s">
+        <v>5499</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5500</v>
+      </c>
+      <c r="J3" t="s">
+        <v>5501</v>
+      </c>
+      <c r="K3" t="s">
+        <v>5502</v>
+      </c>
+      <c r="L3" t="s">
+        <v>5503</v>
+      </c>
+      <c r="M3" t="s">
+        <v>5504</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>5579</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5505</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5506</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5507</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5508</v>
+      </c>
+      <c r="F4" t="s">
+        <v>5509</v>
+      </c>
+      <c r="G4" t="s">
+        <v>5510</v>
+      </c>
+      <c r="H4" t="s">
+        <v>5511</v>
+      </c>
+      <c r="I4" t="s">
+        <v>5512</v>
+      </c>
+      <c r="J4" t="s">
+        <v>5513</v>
+      </c>
+      <c r="K4" t="s">
+        <v>5514</v>
+      </c>
+      <c r="L4" t="s">
+        <v>5515</v>
+      </c>
+      <c r="M4" t="s">
+        <v>5516</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>5580</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5517</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5518</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5519</v>
+      </c>
+      <c r="E5" t="s">
+        <v>5520</v>
+      </c>
+      <c r="F5" t="s">
+        <v>5521</v>
+      </c>
+      <c r="G5" t="s">
+        <v>5522</v>
+      </c>
+      <c r="H5" t="s">
+        <v>5523</v>
+      </c>
+      <c r="I5" t="s">
+        <v>5524</v>
+      </c>
+      <c r="J5" t="s">
+        <v>5525</v>
+      </c>
+      <c r="K5" t="s">
+        <v>5526</v>
+      </c>
+      <c r="L5" t="s">
+        <v>5527</v>
+      </c>
+      <c r="M5" t="s">
+        <v>5528</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>5581</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5529</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5530</v>
+      </c>
+      <c r="D6" t="s">
+        <v>5531</v>
+      </c>
+      <c r="E6" t="s">
+        <v>5532</v>
+      </c>
+      <c r="F6" t="s">
+        <v>5533</v>
+      </c>
+      <c r="G6" t="s">
+        <v>5534</v>
+      </c>
+      <c r="H6" t="s">
+        <v>5535</v>
+      </c>
+      <c r="I6" t="s">
+        <v>5536</v>
+      </c>
+      <c r="J6" t="s">
+        <v>5537</v>
+      </c>
+      <c r="K6" t="s">
+        <v>5538</v>
+      </c>
+      <c r="L6" t="s">
+        <v>5539</v>
+      </c>
+      <c r="M6" t="s">
+        <v>5540</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>5582</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5541</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5542</v>
+      </c>
+      <c r="D7" t="s">
+        <v>5543</v>
+      </c>
+      <c r="E7" t="s">
+        <v>5544</v>
+      </c>
+      <c r="F7" t="s">
+        <v>5545</v>
+      </c>
+      <c r="G7" t="s">
+        <v>5546</v>
+      </c>
+      <c r="H7" t="s">
+        <v>5547</v>
+      </c>
+      <c r="I7" t="s">
+        <v>5548</v>
+      </c>
+      <c r="J7" t="s">
+        <v>5549</v>
+      </c>
+      <c r="K7" t="s">
+        <v>5550</v>
+      </c>
+      <c r="L7" t="s">
+        <v>5551</v>
+      </c>
+      <c r="M7" t="s">
+        <v>5552</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>5583</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5553</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5554</v>
+      </c>
+      <c r="D8" t="s">
+        <v>5555</v>
+      </c>
+      <c r="E8" t="s">
+        <v>5556</v>
+      </c>
+      <c r="F8" t="s">
+        <v>5557</v>
+      </c>
+      <c r="G8" t="s">
+        <v>5558</v>
+      </c>
+      <c r="H8" t="s">
+        <v>5559</v>
+      </c>
+      <c r="I8" t="s">
+        <v>5560</v>
+      </c>
+      <c r="J8" t="s">
+        <v>5561</v>
+      </c>
+      <c r="K8" t="s">
+        <v>5562</v>
+      </c>
+      <c r="L8" t="s">
+        <v>5563</v>
+      </c>
+      <c r="M8" t="s">
+        <v>5564</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>5584</v>
+      </c>
+      <c r="B9" t="s">
+        <v>5565</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5566</v>
+      </c>
+      <c r="D9" t="s">
+        <v>5567</v>
+      </c>
+      <c r="E9" t="s">
+        <v>5568</v>
+      </c>
+      <c r="F9" t="s">
+        <v>5569</v>
+      </c>
+      <c r="G9" t="s">
+        <v>5570</v>
+      </c>
+      <c r="H9" t="s">
+        <v>5571</v>
+      </c>
+      <c r="I9" t="s">
+        <v>5572</v>
+      </c>
+      <c r="J9" t="s">
+        <v>5573</v>
+      </c>
+      <c r="K9" t="s">
+        <v>5574</v>
+      </c>
+      <c r="L9" t="s">
+        <v>5575</v>
+      </c>
+      <c r="M9" t="s">
+        <v>5576</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED33E3D-34B0-43F5-8BE6-6B2BD1300ECE}">
   <dimension ref="A1:CT26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -24602,7 +25291,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3EA498E-20C6-449F-95FE-BF596291895A}">
   <dimension ref="A1:CT26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -32300,7 +32989,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CFB7CB4-7EC9-4208-8994-F244702D542B}">
   <dimension ref="A1:CT26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
